--- a/output/11_11GHz_2+0_시범비교(회신전_참고용).xlsx
+++ b/output/11_11GHz_2+0_시범비교(회신전_참고용).xlsx
@@ -584,7 +584,7 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="9" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -636,13 +636,13 @@
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" s="4" t="n">
         <v>299584</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>299584</v>
+        <v>599168</v>
       </c>
     </row>
     <row r="3">
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4" t="n">
         <v>525000</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>525000</v>
+        <v>1050000</v>
       </c>
     </row>
     <row r="4">
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>3051169</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3051169</v>
+        <v>6102338</v>
       </c>
     </row>
     <row r="5">
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4" t="n">
         <v>3051169</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>3051169</v>
+        <v>6102338</v>
       </c>
     </row>
     <row r="6">
@@ -740,13 +740,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" s="4" t="n">
         <v>174636</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>174636</v>
+        <v>349272</v>
       </c>
     </row>
     <row r="7">
@@ -766,13 +766,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" s="4" t="n">
         <v>2442678</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2442678</v>
+        <v>4885356</v>
       </c>
     </row>
     <row r="8">
@@ -786,7 +786,7 @@
       <c r="D8" s="2" t="inlineStr"/>
       <c r="E8" s="4" t="inlineStr"/>
       <c r="F8" s="4" t="n">
-        <v>9544236</v>
+        <v>19088472</v>
       </c>
     </row>
   </sheetData>
@@ -1869,7 +1869,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="n">
-        <v>9544236</v>
+        <v>19088472</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
